--- a/pensum/ok04/LOM_Ovingsark_Okonomistyring_kap04_Nokkeltall_NY.xlsx
+++ b/pensum/ok04/LOM_Ovingsark_Okonomistyring_kap04_Nokkeltall_NY.xlsx
@@ -1023,7 +1023,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Bok 1. Bedriftene i «Les og tolk» og i scenario C er konstruert for øvingene.</t>
+          <t>Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Økonomistyring for LØM-emnet. Bedriftene i «Les og tolk» og i scenario C er konstruert for øvingene.</t>
         </is>
       </c>
     </row>
@@ -1098,11 +1098,11 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Varekostnad underentreprenør</t>
+          <t>Varekostnad innleide montører</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>3660000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="8">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>7400000</v>
+        <v>10660000</v>
       </c>
     </row>
     <row r="11">
@@ -1622,7 +1622,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 3 og 4. Nordlys Elektro AS er en konstruert casebedrift som brukes i hele Økonomistyring. Dette er nøyaktig det samme resultatet og den samme balansen som i LOM_Ovingsark_Okonomistyring_kap03_Resultat_og_balanse_NY.xlsx.</t>
+          <t>Kilde: Økonomistyring for LØM-emnet, kap. 3 og 4. Nordlys Elektro AS er en konstruert casebedrift som brukes i hele Økonomistyring. Dette er nøyaktig det samme resultatet og den samme balansen som i LOM_Ovingsark_Okonomistyring_kap03_Resultat_og_balanse_NY.xlsx.</t>
         </is>
       </c>
     </row>
@@ -2442,18 +2442,18 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Venter Nordlys lenger på pengene enn grossisten venter på sine?</t>
+          <t>Står pengene bundet lenger enn grossisten finansierer dem? (lagringstid + kredittid kunder − kredittid leverandører)</t>
         </is>
       </c>
       <c r="B58" s="13">
-        <f>IF(C27&gt;C28,"OK — og det er nettopp derfor kassekreditten brukes: du betaler før du får betalt","AVVIK: da finansierer leverandørene driften, og kassekreditten skulle vært unødvendig")</f>
+        <f>IF(C30+C27-C28&gt;0,"OK — og det er nettopp derfor kassekreditten brukes: fra kabelen kjøpes til kunden betaler går det "&amp;TEXT(C30+C27,"0")&amp;" dager, grossisten finansierer "&amp;TEXT(C28,"0")&amp;" av dem, og de siste "&amp;TEXT(C30+C27-C28,"0")&amp;" må Nordlys finansiere selv","AVVIK: da finansierer leverandørene hele driften, og kassekreditten skulle vært unødvendig")</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Her SKAL det stå OK med tallene som ligger inne — og det er et problem, ikke en trøst. Forskjellen mellom de to kredittidene er det kassekreditten dekker.</t>
+          <t>Her SKAL det stå OK med tallene som ligger inne — og det er et problem, ikke en trøst. Dagene Nordlys finansierer selv er det kassekreditten dekker.</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 4.2 til 4.2.4 og tabell 4.2. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
+          <t>Kilde: Økonomistyring for LØM-emnet, kap. 4.2 til 4.2.4 og tabell 4.2. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>11650000</v>
+        <v>8390000</v>
       </c>
     </row>
     <row r="9">
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>7400000</v>
+        <v>10660000</v>
       </c>
     </row>
     <row r="10">
@@ -3917,7 +3917,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Kilde: metode og normtall fra Bok 1 kap. 4.2. Tallene for bedrift B er konstruert for øvingen; bedriftsnavnet er hentet fra casemiljøet rundt Nordlys Elektro AS.</t>
+          <t>Kilde: metode og normtall fra Økonomistyring for LØM-emnet, kap. 4.2. Tallene for bedrift B er konstruert for øvingen; bedriftsnavnet er hentet fra casemiljøet rundt Nordlys Elektro AS.</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 4.2.1 til 4.2.4. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent. De to bedriftene i scenario C er konstruert for øvingen, men utledet: hver av dem er gitt fire nøkkeltall og den samme omsetningen som Nordlys, og alt annet regnes av dem.</t>
+          <t>Kilde: Økonomistyring for LØM-emnet, kap. 4.2.1 til 4.2.4. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent. De to bedriftene i scenario C er konstruert for øvingen, men utledet: hver av dem er gitt fire nøkkeltall og den samme omsetningen som Nordlys, og alt annet regnes av dem.</t>
         </is>
       </c>
     </row>
